--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Nhập kho/Tháng 06/NKBH_KhoVNET(AnhTuanNB)_110626.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Nhập kho/Tháng 06/NKBH_KhoVNET(AnhTuanNB)_110626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Nhập kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205A721F-500E-4DCE-BE7C-A4D6192DEA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB30AFB-D3CD-4D2F-B3C4-3B1444236481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,72 +595,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,6 +608,72 @@
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1100,66 +1100,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="57"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="50"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="49" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="51" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="40" t="s">
         <v>45</v>
       </c>
       <c r="H10" s="32"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="32"/>
-      <c r="G11" s="54"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="32"/>
-      <c r="G12" s="54"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
-      <c r="G13" s="55"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1467,119 +1467,119 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="56"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="60">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="39" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="60">
+      <c r="A3" s="38">
         <v>2</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="60">
+      <c r="A4" s="38">
         <v>3</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="39" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="60">
+      <c r="A5" s="38">
         <v>4</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="39" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="60">
+      <c r="A6" s="38">
         <v>5</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="39" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="60">
+      <c r="A7" s="38">
         <v>6</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="39" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="60">
+      <c r="A8" s="38">
         <v>7</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="39" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="60">
+      <c r="A9" s="38">
         <v>8</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="39" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="60">
+      <c r="A10" s="38">
         <v>9</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="39" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="60">
+      <c r="A11" s="38">
         <v>10</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="60">
+      <c r="A12" s="38">
         <v>11</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="39" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="60">
+      <c r="A13" s="38">
         <v>12</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="39" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="60">
+      <c r="A14" s="38">
         <v>13</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="39" t="s">
         <v>43</v>
       </c>
     </row>
